--- a/Backtest/02-01-24/S&P500stock_02-01-24period252RS90.xlsx
+++ b/Backtest/02-01-24/S&P500stock_02-01-24period252RS90.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="107" uniqueCount="82">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="122" uniqueCount="99">
   <si>
     <t>Stock</t>
   </si>
@@ -130,15 +130,15 @@
     <t>KKR</t>
   </si>
   <si>
+    <t>CEG</t>
+  </si>
+  <si>
     <t>CRM</t>
   </si>
   <si>
     <t>PANW</t>
   </si>
   <si>
-    <t>ABNB</t>
-  </si>
-  <si>
     <t>NVDA</t>
   </si>
   <si>
@@ -157,28 +157,37 @@
     <t>CRWD</t>
   </si>
   <si>
-    <t>CCL</t>
-  </si>
-  <si>
-    <t>BKNG</t>
-  </si>
-  <si>
-    <t>EXPE</t>
+    <t>TDG</t>
+  </si>
+  <si>
+    <t>PH</t>
+  </si>
+  <si>
+    <t>CBOE</t>
   </si>
   <si>
     <t>INTU</t>
   </si>
   <si>
+    <t>SMCI</t>
+  </si>
+  <si>
     <t>CMG</t>
   </si>
   <si>
+    <t>MLM</t>
+  </si>
+  <si>
+    <t>ISRG</t>
+  </si>
+  <si>
     <t>DELL</t>
   </si>
   <si>
     <t>ANET</t>
   </si>
   <si>
-    <t>M</t>
+    <t>GWW</t>
   </si>
   <si>
     <t>inf</t>
@@ -187,34 +196,46 @@
     <t>2024-02-06</t>
   </si>
   <si>
+    <t>2024-02-27</t>
+  </si>
+  <si>
     <t>2024-02-28</t>
   </si>
   <si>
     <t>2024-02-20</t>
   </si>
   <si>
-    <t>2024-02-13</t>
-  </si>
-  <si>
     <t>2024-02-21</t>
   </si>
   <si>
-    <t>2024-02-01</t>
-  </si>
-  <si>
-    <t>2024-01-24</t>
+    <t>2024-04-30</t>
+  </si>
+  <si>
+    <t>2024-04-24</t>
+  </si>
+  <si>
+    <t>2024-04-25</t>
   </si>
   <si>
     <t>2024-03-05</t>
   </si>
   <si>
-    <t>2024-03-27</t>
+    <t>2024-02-08</t>
+  </si>
+  <si>
+    <t>2024-05-02</t>
+  </si>
+  <si>
+    <t>2024-02-02</t>
   </si>
   <si>
     <t>2024-02-22</t>
   </si>
   <si>
-    <t>2024-02-08</t>
+    <t>2024-02-14</t>
+  </si>
+  <si>
+    <t>2024-04-18</t>
   </si>
   <si>
     <t>2024-02-29</t>
@@ -226,40 +247,70 @@
     <t>Financial Services</t>
   </si>
   <si>
+    <t>Utilities</t>
+  </si>
+  <si>
     <t>Technology</t>
   </si>
   <si>
     <t>Consumer Cyclical</t>
   </si>
   <si>
-    <t>Utilities</t>
+    <t>Industrials</t>
+  </si>
+  <si>
+    <t>Basic Materials</t>
+  </si>
+  <si>
+    <t>Healthcare</t>
   </si>
   <si>
     <t>Asset Management</t>
   </si>
   <si>
+    <t>Utilities - Renewable</t>
+  </si>
+  <si>
     <t>Software - Application</t>
   </si>
   <si>
     <t>Software - Infrastructure</t>
   </si>
   <si>
+    <t>Semiconductors</t>
+  </si>
+  <si>
+    <t>Internet Retail</t>
+  </si>
+  <si>
+    <t>Utilities - Independent Power Producers</t>
+  </si>
+  <si>
     <t>Travel Services</t>
   </si>
   <si>
-    <t>Semiconductors</t>
-  </si>
-  <si>
-    <t>Internet Retail</t>
-  </si>
-  <si>
-    <t>Utilities - Independent Power Producers</t>
+    <t>Aerospace &amp; Defense</t>
+  </si>
+  <si>
+    <t>Specialty Industrial Machinery</t>
+  </si>
+  <si>
+    <t>Financial Data &amp; Stock Exchanges</t>
+  </si>
+  <si>
+    <t>Computer Hardware</t>
   </si>
   <si>
     <t>Restaurants</t>
   </si>
   <si>
-    <t>Computer Hardware</t>
+    <t>Building Materials</t>
+  </si>
+  <si>
+    <t>Medical Instruments &amp; Supplies</t>
+  </si>
+  <si>
+    <t>Industrial Distribution</t>
   </si>
 </sst>
 </file>
@@ -617,7 +668,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AK18"/>
+  <dimension ref="A1:AK22"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:37">
@@ -738,46 +789,43 @@
         <v>37</v>
       </c>
       <c r="B2">
-        <v>94.98997995991984</v>
+        <v>94.58917835671342</v>
       </c>
       <c r="C2">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="D2">
-        <v>82.84999999999999</v>
+        <v>86.58</v>
       </c>
       <c r="E2">
-        <v>1.52</v>
+        <v>1.26</v>
       </c>
       <c r="F2">
-        <v>-0.1414173730819506</v>
+        <v>-0.4126485776572325</v>
       </c>
       <c r="G2">
-        <v>2.09</v>
+        <v>1.83</v>
       </c>
       <c r="H2">
-        <v>0.1506115215234779</v>
+        <v>0.03265521346575155</v>
       </c>
       <c r="I2">
-        <v>82.7739990234375</v>
+        <v>86.72200012207031</v>
       </c>
       <c r="J2">
-        <v>80.03900032043457</v>
+        <v>83.22099990844727</v>
       </c>
       <c r="K2">
-        <v>69.52879981994629</v>
+        <v>79.52819961547851</v>
       </c>
       <c r="L2">
-        <v>59.7191499710083</v>
+        <v>63.12919996261596</v>
       </c>
       <c r="M2">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="N2">
-        <v>1.19</v>
-      </c>
-      <c r="O2" t="s">
-        <v>54</v>
+        <v>1.09</v>
       </c>
       <c r="P2">
         <v>9</v>
@@ -795,19 +843,19 @@
         <v>12.22222222222222</v>
       </c>
       <c r="U2" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V2" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W2" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X2">
-        <v>45.26</v>
+        <v>47.46</v>
       </c>
       <c r="Y2">
-        <v>85.66</v>
+        <v>88.51000000000001</v>
       </c>
       <c r="Z2">
         <v>56</v>
@@ -834,16 +882,16 @@
         <v>37.04</v>
       </c>
       <c r="AH2" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="AI2" t="s">
-        <v>69</v>
+        <v>76</v>
       </c>
       <c r="AJ2" t="s">
-        <v>73</v>
+        <v>83</v>
       </c>
       <c r="AK2">
-        <v>86.52833845284135</v>
+        <v>85.93517979930812</v>
       </c>
     </row>
     <row r="3" spans="1:37">
@@ -851,44 +899,44 @@
         <v>38</v>
       </c>
       <c r="B3">
-        <v>97.1943887775551</v>
+        <v>90.98196392785572</v>
       </c>
       <c r="C3">
-        <v>114</v>
+        <v>326</v>
       </c>
       <c r="D3">
-        <v>263.14</v>
+        <v>122</v>
       </c>
       <c r="E3">
-        <v>1.47</v>
+        <v>1.59</v>
       </c>
       <c r="F3">
-        <v>-0.2459432575338273</v>
+        <v>-0.2008223077931864</v>
       </c>
       <c r="G3">
-        <v>1.81</v>
+        <v>2</v>
       </c>
       <c r="H3">
-        <v>-0.3688890889488085</v>
+        <v>0.199196802141085</v>
       </c>
       <c r="I3">
-        <v>265.6</v>
+        <v>121.3419998168945</v>
       </c>
       <c r="J3">
-        <v>258.9290016174317</v>
+        <v>116.5254997253418</v>
       </c>
       <c r="K3">
-        <v>231.7774008178711</v>
+        <v>117.664599609375</v>
       </c>
       <c r="L3">
-        <v>214.0647497558594</v>
+        <v>103.7070748901367</v>
       </c>
       <c r="M3">
+        <v>1.04</v>
+      </c>
+      <c r="N3">
         <v>1.03</v>
       </c>
-      <c r="N3">
-        <v>1.15</v>
-      </c>
       <c r="P3">
         <v>0</v>
       </c>
@@ -905,55 +953,55 @@
         <v>0</v>
       </c>
       <c r="U3" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W3" t="b">
         <v>1</v>
       </c>
       <c r="X3">
-        <v>129.5</v>
+        <v>71.16</v>
       </c>
       <c r="Y3">
-        <v>268.36</v>
+        <v>127.24</v>
       </c>
       <c r="Z3">
-        <v>197.01</v>
+        <v>35.23</v>
       </c>
       <c r="AA3">
-        <v>16.98</v>
+        <v>0.55</v>
       </c>
       <c r="AB3">
-        <v>1562.5</v>
+        <v>1167.35</v>
       </c>
       <c r="AC3">
-        <v>1360</v>
+        <v>2170</v>
       </c>
       <c r="AD3">
-        <v>2.11</v>
+        <v>5.75</v>
       </c>
       <c r="AE3">
-        <v>-3.08</v>
+        <v>-11.67</v>
       </c>
       <c r="AF3">
-        <v>550</v>
+        <v>786.21</v>
       </c>
       <c r="AG3">
-        <v>300</v>
+        <v>190</v>
       </c>
       <c r="AH3" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="AI3" t="s">
-        <v>70</v>
+        <v>77</v>
       </c>
       <c r="AJ3" t="s">
-        <v>74</v>
+        <v>84</v>
       </c>
       <c r="AK3">
-        <v>82.64566073279751</v>
+        <v>84.10455064845821</v>
       </c>
     </row>
     <row r="4" spans="1:37">
@@ -961,109 +1009,109 @@
         <v>39</v>
       </c>
       <c r="B4">
-        <v>97.59519038076152</v>
+        <v>95.99198396793587</v>
       </c>
       <c r="C4">
-        <v>92</v>
+        <v>140</v>
       </c>
       <c r="D4">
-        <v>147.44</v>
+        <v>281.09</v>
       </c>
       <c r="E4">
-        <v>1.92</v>
+        <v>1.56</v>
       </c>
       <c r="F4">
-        <v>0.6947897025330617</v>
+        <v>-0.2200792414171906</v>
       </c>
       <c r="G4">
-        <v>2.24</v>
+        <v>1.83</v>
       </c>
       <c r="H4">
-        <v>0.428915419990775</v>
+        <v>0.03265521346575155</v>
       </c>
       <c r="I4">
-        <v>148.6989990234375</v>
+        <v>283.1299987792969</v>
       </c>
       <c r="J4">
-        <v>149.6349983215332</v>
+        <v>271.4709983825684</v>
       </c>
       <c r="K4">
-        <v>135.8483993530273</v>
+        <v>258.2996002197266</v>
       </c>
       <c r="L4">
-        <v>117.4182497024536</v>
+        <v>222.3545495605469</v>
       </c>
       <c r="M4">
-        <v>0.99</v>
+        <v>1.04</v>
       </c>
       <c r="N4">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="P4">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="Q4">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="R4">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="S4">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="T4">
-        <v>12.77777777777778</v>
+        <v>1.111111111111111</v>
       </c>
       <c r="U4" t="b">
         <v>1</v>
       </c>
       <c r="V4" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W4" t="b">
         <v>1</v>
       </c>
       <c r="X4">
-        <v>66.11</v>
+        <v>159.66</v>
       </c>
       <c r="Y4">
-        <v>159</v>
+        <v>289.29</v>
       </c>
       <c r="Z4">
-        <v>42.5</v>
+        <v>197.01</v>
       </c>
       <c r="AA4">
-        <v>-315.95</v>
+        <v>16.98</v>
       </c>
       <c r="AB4">
-        <v>1105</v>
+        <v>1562.5</v>
       </c>
       <c r="AC4">
-        <v>125</v>
+        <v>1360</v>
       </c>
       <c r="AD4">
-        <v>8.949999999999999</v>
+        <v>2.11</v>
       </c>
       <c r="AE4">
-        <v>-16</v>
+        <v>-3.08</v>
       </c>
       <c r="AF4">
-        <v>114.29</v>
+        <v>550</v>
       </c>
       <c r="AG4">
-        <v>25</v>
+        <v>300</v>
       </c>
       <c r="AH4" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="AI4" t="s">
-        <v>70</v>
+        <v>78</v>
       </c>
       <c r="AJ4" t="s">
-        <v>75</v>
+        <v>85</v>
       </c>
       <c r="AK4">
-        <v>71.18543227281737</v>
+        <v>83.85513350385045</v>
       </c>
     </row>
     <row r="5" spans="1:37">
@@ -1071,61 +1119,61 @@
         <v>40</v>
       </c>
       <c r="B5">
-        <v>91.18236472945893</v>
+        <v>98.39679358717434</v>
       </c>
       <c r="C5">
-        <v>110</v>
+        <v>136</v>
       </c>
       <c r="D5">
-        <v>136.14</v>
+        <v>169.26</v>
       </c>
       <c r="E5">
-        <v>2.27</v>
+        <v>1.81</v>
       </c>
       <c r="F5">
-        <v>1.426470893696198</v>
+        <v>-0.05960479455048907</v>
       </c>
       <c r="G5">
-        <v>2.37</v>
+        <v>2.18</v>
       </c>
       <c r="H5">
-        <v>0.6701121319957651</v>
+        <v>0.3755349548561442</v>
       </c>
       <c r="I5">
-        <v>137.8420013427734</v>
+        <v>171.2280029296875</v>
       </c>
       <c r="J5">
-        <v>140.3435005187988</v>
+        <v>162.1352485656738</v>
       </c>
       <c r="K5">
-        <v>129.362799987793</v>
+        <v>151.9205987548828</v>
       </c>
       <c r="L5">
-        <v>127.5602751541138</v>
+        <v>124.1916996383667</v>
       </c>
       <c r="M5">
-        <v>0.98</v>
+        <v>1.06</v>
       </c>
       <c r="N5">
-        <v>1.07</v>
+        <v>1.13</v>
       </c>
       <c r="P5">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="Q5">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="R5">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="S5">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="T5">
-        <v>0</v>
+        <v>10.55555555555556</v>
       </c>
       <c r="U5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V5" t="b">
         <v>0</v>
@@ -1134,46 +1182,46 @@
         <v>1</v>
       </c>
       <c r="X5">
-        <v>82.29000000000001</v>
+        <v>77.06</v>
       </c>
       <c r="Y5">
-        <v>154.95</v>
+        <v>175.3</v>
       </c>
       <c r="Z5">
-        <v>90.56</v>
+        <v>42.5</v>
       </c>
       <c r="AA5">
-        <v>-624.91</v>
+        <v>-315.95</v>
       </c>
       <c r="AB5">
-        <v>173.72</v>
+        <v>1105</v>
       </c>
       <c r="AC5">
-        <v>1239.22</v>
+        <v>125</v>
       </c>
       <c r="AD5">
-        <v>47.94</v>
+        <v>8.949999999999999</v>
       </c>
       <c r="AE5">
-        <v>569.61</v>
+        <v>-16</v>
       </c>
       <c r="AF5">
-        <v>466.67</v>
+        <v>114.29</v>
       </c>
       <c r="AG5">
-        <v>-64.70999999999999</v>
+        <v>25</v>
       </c>
       <c r="AH5" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="AI5" t="s">
-        <v>71</v>
+        <v>78</v>
       </c>
       <c r="AJ5" t="s">
-        <v>76</v>
+        <v>86</v>
       </c>
       <c r="AK5">
-        <v>57.78840164093568</v>
+        <v>70.43301171000144</v>
       </c>
     </row>
     <row r="6" spans="1:37">
@@ -1181,61 +1229,61 @@
         <v>41</v>
       </c>
       <c r="B6">
-        <v>100</v>
+        <v>99.79959919839679</v>
       </c>
       <c r="C6">
         <v>1</v>
       </c>
       <c r="D6">
-        <v>49.52</v>
+        <v>61.53</v>
       </c>
       <c r="E6">
-        <v>1.72</v>
+        <v>1.98</v>
       </c>
       <c r="F6">
-        <v>0.2766861647255556</v>
+        <v>0.04951782931886792</v>
       </c>
       <c r="G6">
-        <v>2.09</v>
+        <v>1.89</v>
       </c>
       <c r="H6">
-        <v>0.1506115215234779</v>
+        <v>0.09143459770410439</v>
       </c>
       <c r="I6">
-        <v>49.31399993896484</v>
+        <v>61.8827995300293</v>
       </c>
       <c r="J6">
-        <v>48.07049999237061</v>
+        <v>56.66374969482422</v>
       </c>
       <c r="K6">
-        <v>46.68486000061035</v>
+        <v>51.5993798828125</v>
       </c>
       <c r="L6">
-        <v>40.59727991104126</v>
+        <v>43.69105487823487</v>
       </c>
       <c r="M6">
-        <v>1.03</v>
+        <v>1.09</v>
       </c>
       <c r="N6">
-        <v>1.06</v>
+        <v>1.2</v>
       </c>
       <c r="P6">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="Q6">
         <v>0</v>
       </c>
       <c r="R6">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="S6">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="T6">
-        <v>7.222222222222221</v>
+        <v>13.88888888888889</v>
       </c>
       <c r="U6" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V6" t="b">
         <v>1</v>
@@ -1244,10 +1292,10 @@
         <v>1</v>
       </c>
       <c r="X6">
-        <v>14.03</v>
+        <v>18.95</v>
       </c>
       <c r="Y6">
-        <v>50.55</v>
+        <v>63.49</v>
       </c>
       <c r="Z6">
         <v>1017.05</v>
@@ -1274,16 +1322,16 @@
         <v>43.1</v>
       </c>
       <c r="AH6" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="AI6" t="s">
-        <v>70</v>
+        <v>78</v>
       </c>
       <c r="AJ6" t="s">
-        <v>77</v>
+        <v>87</v>
       </c>
       <c r="AK6">
-        <v>56.15845655525175</v>
+        <v>67.66073736034078</v>
       </c>
     </row>
     <row r="7" spans="1:37">
@@ -1291,43 +1339,43 @@
         <v>42</v>
       </c>
       <c r="B7">
-        <v>95.39078156312625</v>
+        <v>93.38677354709419</v>
       </c>
       <c r="C7">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D7">
-        <v>151.94</v>
+        <v>155.2</v>
       </c>
       <c r="E7">
-        <v>1.19</v>
+        <v>1.39</v>
       </c>
       <c r="F7">
-        <v>-0.8312882104643361</v>
+        <v>-0.3292018652865478</v>
       </c>
       <c r="G7">
-        <v>1.79</v>
+        <v>1.26</v>
       </c>
       <c r="H7">
-        <v>-0.4059962754111147</v>
+        <v>-0.525748936798602</v>
       </c>
       <c r="I7">
-        <v>153.0980010986328</v>
+        <v>158.4659973144531</v>
       </c>
       <c r="J7">
-        <v>149.823999786377</v>
+        <v>153.7994995117188</v>
       </c>
       <c r="K7">
-        <v>143.0456002807617</v>
+        <v>150.764599609375</v>
       </c>
       <c r="L7">
-        <v>127.7337503814697</v>
+        <v>133.3232503509522</v>
       </c>
       <c r="M7">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="N7">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="P7">
         <v>0</v>
@@ -1351,13 +1399,13 @@
         <v>0</v>
       </c>
       <c r="W7" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X7">
-        <v>81.43000000000001</v>
+        <v>88.12</v>
       </c>
       <c r="Y7">
-        <v>155.63</v>
+        <v>161.73</v>
       </c>
       <c r="Z7">
         <v>1342.13</v>
@@ -1384,16 +1432,16 @@
         <v>933.33</v>
       </c>
       <c r="AH7" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="AI7" t="s">
-        <v>71</v>
+        <v>79</v>
       </c>
       <c r="AJ7" t="s">
-        <v>78</v>
+        <v>88</v>
       </c>
       <c r="AK7">
-        <v>54.82124900203854</v>
+        <v>64.08436606455442</v>
       </c>
     </row>
     <row r="8" spans="1:37">
@@ -1401,49 +1449,49 @@
         <v>43</v>
       </c>
       <c r="B8">
-        <v>90.18036072144288</v>
+        <v>96.79358717434869</v>
       </c>
       <c r="C8">
-        <v>194</v>
+        <v>259</v>
       </c>
       <c r="D8">
-        <v>38.52</v>
+        <v>41.03</v>
       </c>
       <c r="E8">
-        <v>1.36</v>
+        <v>1.31</v>
       </c>
       <c r="F8">
-        <v>-0.4759002033279555</v>
+        <v>-0.3805536882838921</v>
       </c>
       <c r="G8">
-        <v>1.39</v>
+        <v>1.26</v>
       </c>
       <c r="H8">
-        <v>-1.148140004657239</v>
+        <v>-0.525748936798602</v>
       </c>
       <c r="I8">
-        <v>38.38800048828125</v>
+        <v>40.80599975585938</v>
       </c>
       <c r="J8">
-        <v>37.575</v>
+        <v>39.60749988555908</v>
       </c>
       <c r="K8">
-        <v>35.48920028686523</v>
+        <v>37.9323999786377</v>
       </c>
       <c r="L8">
-        <v>29.43720009803772</v>
+        <v>31.05020008087158</v>
       </c>
       <c r="M8">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="N8">
         <v>1.08</v>
       </c>
       <c r="P8">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q8">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="R8">
         <v>0</v>
@@ -1452,7 +1500,7 @@
         <v>0</v>
       </c>
       <c r="T8">
-        <v>0</v>
+        <v>2.777777777777778</v>
       </c>
       <c r="U8" t="b">
         <v>1</v>
@@ -1467,7 +1515,7 @@
         <v>21.18</v>
       </c>
       <c r="Y8">
-        <v>38.9</v>
+        <v>41.66</v>
       </c>
       <c r="Z8">
         <v>12.35</v>
@@ -1494,16 +1542,16 @@
         <v>315</v>
       </c>
       <c r="AH8" t="s">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="AI8" t="s">
-        <v>72</v>
+        <v>77</v>
       </c>
       <c r="AJ8" t="s">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="AK8">
-        <v>51.63920838692619</v>
+        <v>59.14194207035997</v>
       </c>
     </row>
     <row r="9" spans="1:37">
@@ -1511,49 +1559,49 @@
         <v>44</v>
       </c>
       <c r="B9">
-        <v>95.59118236472945</v>
+        <v>96.39278557114228</v>
       </c>
       <c r="C9">
-        <v>407</v>
+        <v>300</v>
       </c>
       <c r="D9">
-        <v>706.49</v>
+        <v>765.4</v>
       </c>
       <c r="E9">
-        <v>1.53</v>
+        <v>1.37</v>
       </c>
       <c r="F9">
-        <v>-0.1205121961915753</v>
+        <v>-0.3420398210358838</v>
       </c>
       <c r="G9">
-        <v>1.67</v>
+        <v>1.38</v>
       </c>
       <c r="H9">
-        <v>-0.6286393941849521</v>
+        <v>-0.4081901683218961</v>
       </c>
       <c r="I9">
-        <v>702.297998046875</v>
+        <v>774.9</v>
       </c>
       <c r="J9">
-        <v>698.6484954833984</v>
+        <v>734.1079956054688</v>
       </c>
       <c r="K9">
-        <v>649.7777966308594</v>
+        <v>707.5269958496094</v>
       </c>
       <c r="L9">
-        <v>559.5369001770019</v>
+        <v>588.8078999328613</v>
       </c>
       <c r="M9">
-        <v>1.01</v>
+        <v>1.06</v>
       </c>
       <c r="N9">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="P9">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="Q9">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="R9">
         <v>1</v>
@@ -1562,58 +1610,58 @@
         <v>0</v>
       </c>
       <c r="T9">
-        <v>8.333333333333332</v>
+        <v>12.22222222222222</v>
       </c>
       <c r="U9" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V9" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W9" t="b">
         <v>1</v>
       </c>
       <c r="X9">
-        <v>353.62</v>
+        <v>405.37</v>
       </c>
       <c r="Y9">
-        <v>720.6799999999999</v>
+        <v>789.92</v>
       </c>
       <c r="Z9">
-        <v>115.3</v>
+        <v>145.25</v>
       </c>
       <c r="AA9">
-        <v>-2701.39</v>
+        <v>-6625</v>
       </c>
       <c r="AB9">
-        <v>349.71</v>
+        <v>260.85</v>
       </c>
       <c r="AC9">
-        <v>59.46</v>
+        <v>94.59</v>
       </c>
       <c r="AD9">
-        <v>3.37</v>
+        <v>3.87</v>
       </c>
       <c r="AE9">
+        <v>22.03</v>
+      </c>
+      <c r="AF9">
         <v>-76.95</v>
       </c>
-      <c r="AF9">
+      <c r="AG9">
         <v>591.89</v>
       </c>
-      <c r="AG9">
-        <v>0</v>
-      </c>
       <c r="AH9" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="AI9" t="s">
-        <v>70</v>
+        <v>78</v>
       </c>
       <c r="AJ9" t="s">
-        <v>74</v>
+        <v>85</v>
       </c>
       <c r="AK9">
-        <v>49.59683613952767</v>
+        <v>57.90728992112621</v>
       </c>
     </row>
     <row r="10" spans="1:37">
@@ -1621,43 +1669,43 @@
         <v>45</v>
       </c>
       <c r="B10">
-        <v>99.19839679358718</v>
+        <v>97.59519038076152</v>
       </c>
       <c r="C10">
-        <v>200</v>
+        <v>222</v>
       </c>
       <c r="D10">
-        <v>129.49</v>
+        <v>127.5</v>
       </c>
       <c r="E10">
-        <v>1.74</v>
+        <v>1.71</v>
       </c>
       <c r="F10">
-        <v>0.3184965185063062</v>
+        <v>-0.1237945732971698</v>
       </c>
       <c r="G10">
-        <v>2.02</v>
+        <v>2.12</v>
       </c>
       <c r="H10">
-        <v>0.02073636890540649</v>
+        <v>0.3167555706177911</v>
       </c>
       <c r="I10">
-        <v>129.3140014648438</v>
+        <v>126.4839996337891</v>
       </c>
       <c r="J10">
-        <v>122.0965003967285</v>
+        <v>124.1184993743896</v>
       </c>
       <c r="K10">
-        <v>105.521600189209</v>
+        <v>119.9103999328613</v>
       </c>
       <c r="L10">
-        <v>91.72154994964599</v>
+        <v>98.1644998550415</v>
       </c>
       <c r="M10">
-        <v>1.06</v>
+        <v>1.02</v>
       </c>
       <c r="N10">
-        <v>1.23</v>
+        <v>1.05</v>
       </c>
       <c r="P10">
         <v>3</v>
@@ -1675,16 +1723,16 @@
         <v>2.777777777777778</v>
       </c>
       <c r="U10" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V10" t="b">
         <v>1</v>
       </c>
       <c r="W10" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X10">
-        <v>47.94</v>
+        <v>59.37</v>
       </c>
       <c r="Y10">
         <v>130.97</v>
@@ -1714,16 +1762,16 @@
         <v>90.26000000000001</v>
       </c>
       <c r="AH10" t="s">
-        <v>61</v>
+        <v>66</v>
       </c>
       <c r="AI10" t="s">
-        <v>71</v>
+        <v>79</v>
       </c>
       <c r="AJ10" t="s">
-        <v>76</v>
+        <v>90</v>
       </c>
       <c r="AK10">
-        <v>45.99811344525102</v>
+        <v>53.67064369838766</v>
       </c>
     </row>
     <row r="11" spans="1:37">
@@ -1731,49 +1779,49 @@
         <v>46</v>
       </c>
       <c r="B11">
-        <v>98.79759519038076</v>
+        <v>99.59919839679358</v>
       </c>
       <c r="C11">
-        <v>229</v>
+        <v>203</v>
       </c>
       <c r="D11">
-        <v>255.32</v>
+        <v>292.5</v>
       </c>
       <c r="E11">
-        <v>1.06</v>
+        <v>2.45</v>
       </c>
       <c r="F11">
-        <v>-1.103055510039215</v>
+        <v>0.351209789428267</v>
       </c>
       <c r="G11">
-        <v>2.13</v>
+        <v>2.21</v>
       </c>
       <c r="H11">
-        <v>0.2248258944480903</v>
+        <v>0.4049246469753205</v>
       </c>
       <c r="I11">
-        <v>256.45400390625</v>
+        <v>295.6580017089844</v>
       </c>
       <c r="J11">
-        <v>250.2759986877441</v>
+        <v>281.656999206543</v>
       </c>
       <c r="K11">
-        <v>217.3352005004883</v>
+        <v>256.4693994140625</v>
       </c>
       <c r="L11">
-        <v>166.1014501190186</v>
+        <v>181.5655499649048</v>
       </c>
       <c r="M11">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="N11">
-        <v>1.18</v>
+        <v>1.15</v>
       </c>
       <c r="P11">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="Q11">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="R11">
         <v>3</v>
@@ -1782,10 +1830,10 @@
         <v>2</v>
       </c>
       <c r="T11">
-        <v>12.22222222222222</v>
+        <v>10</v>
       </c>
       <c r="U11" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V11" t="b">
         <v>0</v>
@@ -1794,10 +1842,10 @@
         <v>1</v>
       </c>
       <c r="X11">
-        <v>92.25</v>
+        <v>100.74</v>
       </c>
       <c r="Y11">
-        <v>261.81</v>
+        <v>307.55</v>
       </c>
       <c r="Z11">
         <v>43.1</v>
@@ -1818,22 +1866,22 @@
         <v>175</v>
       </c>
       <c r="AF11" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="AG11">
         <v>100</v>
       </c>
       <c r="AH11" t="s">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="AI11" t="s">
-        <v>70</v>
+        <v>78</v>
       </c>
       <c r="AJ11" t="s">
-        <v>75</v>
+        <v>86</v>
       </c>
       <c r="AK11">
-        <v>45.36212434152558</v>
+        <v>51.72571776711951</v>
       </c>
     </row>
     <row r="12" spans="1:37">
@@ -1841,109 +1889,109 @@
         <v>47</v>
       </c>
       <c r="B12">
-        <v>98.39679358717434</v>
+        <v>93.5871743486974</v>
       </c>
       <c r="C12">
-        <v>12</v>
+        <v>490</v>
       </c>
       <c r="D12">
-        <v>18.54</v>
+        <v>1092.68</v>
       </c>
       <c r="E12">
-        <v>2.72</v>
+        <v>1</v>
       </c>
       <c r="F12">
-        <v>2.367203853763087</v>
+        <v>-0.5795420023986021</v>
       </c>
       <c r="G12">
-        <v>2.86</v>
+        <v>1.53</v>
       </c>
       <c r="H12">
-        <v>1.579238200322266</v>
+        <v>-0.2612417077260135</v>
       </c>
       <c r="I12">
-        <v>18.6580005645752</v>
+        <v>1084.339990234375</v>
       </c>
       <c r="J12">
-        <v>18.04300022125244</v>
+        <v>1039.328991699219</v>
       </c>
       <c r="K12">
-        <v>14.97760011672974</v>
+        <v>1005.147998046875</v>
       </c>
       <c r="L12">
-        <v>13.97525002002716</v>
+        <v>887.7636505126953</v>
       </c>
       <c r="M12">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="N12">
-        <v>1.25</v>
+        <v>1.08</v>
       </c>
       <c r="P12">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="Q12">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="R12">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S12">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T12">
-        <v>9.444444444444446</v>
+        <v>12.22222222222222</v>
       </c>
       <c r="U12" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V12" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W12" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X12">
-        <v>7.7</v>
+        <v>686.46</v>
       </c>
       <c r="Y12">
-        <v>19.74</v>
+        <v>1100</v>
       </c>
       <c r="Z12">
-        <v>19.01</v>
+        <v>48.23</v>
       </c>
       <c r="AA12">
-        <v>-0.05</v>
+        <v>1.19</v>
       </c>
       <c r="AB12">
-        <v>98.95</v>
+        <v>31.68</v>
       </c>
       <c r="AC12">
-        <v>92.73</v>
+        <v>117.42</v>
       </c>
       <c r="AD12">
-        <v>-0.71</v>
+        <v>-20.93</v>
       </c>
       <c r="AE12">
-        <v>-104.71</v>
+        <v>17.92</v>
       </c>
       <c r="AF12">
-        <v>365.62</v>
+        <v>15.41</v>
       </c>
       <c r="AG12">
-        <v>41.82</v>
+        <v>59.76</v>
       </c>
       <c r="AH12" t="s">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="AI12" t="s">
-        <v>71</v>
+        <v>80</v>
       </c>
       <c r="AJ12" t="s">
-        <v>76</v>
+        <v>91</v>
       </c>
       <c r="AK12">
-        <v>39.87327624110723</v>
+        <v>42.56738508018305</v>
       </c>
     </row>
     <row r="13" spans="1:37">
@@ -1951,49 +1999,49 @@
         <v>48</v>
       </c>
       <c r="B13">
-        <v>94.18837675350701</v>
+        <v>90.38076152304609</v>
       </c>
       <c r="C13">
-        <v>483</v>
+        <v>418</v>
       </c>
       <c r="D13">
-        <v>3547.22</v>
+        <v>464.5</v>
       </c>
       <c r="E13">
-        <v>1.03</v>
+        <v>1.15</v>
       </c>
       <c r="F13">
-        <v>-1.165771040710341</v>
+        <v>-0.4832573342785813</v>
       </c>
       <c r="G13">
-        <v>1.44</v>
+        <v>1.05</v>
       </c>
       <c r="H13">
-        <v>-1.055372038501473</v>
+        <v>-0.7314767816328376</v>
       </c>
       <c r="I13">
-        <v>3546.9359375</v>
+        <v>472.4499938964844</v>
       </c>
       <c r="J13">
-        <v>3395.371496582031</v>
+        <v>463.9399978637695</v>
       </c>
       <c r="K13">
-        <v>3145.728598632812</v>
+        <v>451.8435998535156</v>
       </c>
       <c r="L13">
-        <v>2907.076697998047</v>
+        <v>396.9172998046875</v>
       </c>
       <c r="M13">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="N13">
-        <v>1.13</v>
+        <v>1.05</v>
       </c>
       <c r="P13">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="Q13">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="R13">
         <v>0</v>
@@ -2002,58 +2050,58 @@
         <v>0</v>
       </c>
       <c r="T13">
-        <v>6.11111111111111</v>
+        <v>0</v>
       </c>
       <c r="U13" t="b">
         <v>1</v>
       </c>
       <c r="V13" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W13" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X13">
-        <v>1974.58</v>
+        <v>300.86</v>
       </c>
       <c r="Y13">
-        <v>3580.62</v>
+        <v>479.14</v>
       </c>
       <c r="Z13">
-        <v>110.98</v>
+        <v>50.78</v>
       </c>
       <c r="AA13">
-        <v>0.54</v>
+        <v>2.98</v>
       </c>
       <c r="AB13">
-        <v>56.24</v>
+        <v>42.37</v>
       </c>
       <c r="AC13">
-        <v>131.16</v>
+        <v>64.61</v>
       </c>
       <c r="AD13">
-        <v>-401.76</v>
+        <v>6.16</v>
       </c>
       <c r="AE13">
-        <v>100.85</v>
+        <v>-8.15</v>
       </c>
       <c r="AF13">
-        <v>397.31</v>
+        <v>19.74</v>
       </c>
       <c r="AG13">
-        <v>-76.86</v>
+        <v>49.68</v>
       </c>
       <c r="AH13" t="s">
-        <v>65</v>
+        <v>69</v>
       </c>
       <c r="AI13" t="s">
-        <v>71</v>
+        <v>80</v>
       </c>
       <c r="AJ13" t="s">
-        <v>76</v>
+        <v>92</v>
       </c>
       <c r="AK13">
-        <v>33.66460599456133</v>
+        <v>31.74647474076485</v>
       </c>
     </row>
     <row r="14" spans="1:37">
@@ -2061,49 +2109,49 @@
         <v>49</v>
       </c>
       <c r="B14">
-        <v>94.38877755511022</v>
+        <v>91.38276553106212</v>
       </c>
       <c r="C14">
-        <v>245</v>
+        <v>421</v>
       </c>
       <c r="D14">
-        <v>151.79</v>
+        <v>183.85</v>
       </c>
       <c r="E14">
-        <v>1.71</v>
+        <v>1.15</v>
       </c>
       <c r="F14">
-        <v>0.2557809878351802</v>
+        <v>-0.4832573342785813</v>
       </c>
       <c r="G14">
-        <v>3.19</v>
+        <v>1.26</v>
       </c>
       <c r="H14">
-        <v>2.191506776950319</v>
+        <v>-0.525748936798602</v>
       </c>
       <c r="I14">
-        <v>153.3539978027344</v>
+        <v>185.1459991455078</v>
       </c>
       <c r="J14">
-        <v>147.3180000305176</v>
+        <v>181.9964996337891</v>
       </c>
       <c r="K14">
-        <v>128.1291998291016</v>
+        <v>179.5001995849609</v>
       </c>
       <c r="L14">
-        <v>109.369349937439</v>
+        <v>155.6491997528076</v>
       </c>
       <c r="M14">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="N14">
-        <v>1.2</v>
+        <v>1.03</v>
       </c>
       <c r="P14">
         <v>0</v>
       </c>
       <c r="Q14">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R14">
         <v>0</v>
@@ -2112,58 +2160,58 @@
         <v>0</v>
       </c>
       <c r="T14">
-        <v>1.111111111111111</v>
+        <v>0</v>
       </c>
       <c r="U14" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V14" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W14" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X14">
-        <v>84.2</v>
+        <v>116.11</v>
       </c>
       <c r="Y14">
-        <v>155.84</v>
+        <v>190.16</v>
       </c>
       <c r="Z14">
-        <v>15.23</v>
+        <v>16.57</v>
       </c>
       <c r="AA14">
-        <v>12.21</v>
+        <v>3.49</v>
       </c>
       <c r="AB14">
-        <v>36.88</v>
+        <v>78.13</v>
       </c>
       <c r="AC14">
-        <v>161.4</v>
+        <v>29.8</v>
       </c>
       <c r="AD14">
-        <v>10.42</v>
+        <v>5.5</v>
       </c>
       <c r="AE14">
-        <v>13.74</v>
+        <v>24.05</v>
       </c>
       <c r="AF14">
-        <v>375.79</v>
+        <v>-3.07</v>
       </c>
       <c r="AG14">
-        <v>-183.33</v>
+        <v>7.95</v>
       </c>
       <c r="AH14" t="s">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="AI14" t="s">
-        <v>71</v>
+        <v>76</v>
       </c>
       <c r="AJ14" t="s">
-        <v>76</v>
+        <v>93</v>
       </c>
       <c r="AK14">
-        <v>26.72639337933549</v>
+        <v>31.09941062718575</v>
       </c>
     </row>
     <row r="15" spans="1:37">
@@ -2174,43 +2222,43 @@
         <v>92.18436873747495</v>
       </c>
       <c r="C15">
-        <v>367</v>
+        <v>403</v>
       </c>
       <c r="D15">
-        <v>625.03</v>
+        <v>631.33</v>
       </c>
       <c r="E15">
-        <v>1.07</v>
+        <v>1.27</v>
       </c>
       <c r="F15">
-        <v>-1.08215033314884</v>
+        <v>-0.4062295997825644</v>
       </c>
       <c r="G15">
-        <v>1.49</v>
+        <v>1.35</v>
       </c>
       <c r="H15">
-        <v>-0.9626040723457078</v>
+        <v>-0.4375798604410724</v>
       </c>
       <c r="I15">
-        <v>626.2180053710938</v>
+        <v>642.9559936523438</v>
       </c>
       <c r="J15">
-        <v>601.8309997558594</v>
+        <v>617.7175018310547</v>
       </c>
       <c r="K15">
-        <v>557.1563995361328</v>
+        <v>601.6971997070312</v>
       </c>
       <c r="L15">
-        <v>494.444398803711</v>
+        <v>513.8619992065429</v>
       </c>
       <c r="M15">
         <v>1.04</v>
       </c>
       <c r="N15">
-        <v>1.12</v>
+        <v>1.07</v>
       </c>
       <c r="P15">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="Q15">
         <v>0</v>
@@ -2222,22 +2270,22 @@
         <v>0</v>
       </c>
       <c r="T15">
-        <v>3.888888888888888</v>
+        <v>5.555555555555555</v>
       </c>
       <c r="U15" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V15" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W15" t="b">
         <v>1</v>
       </c>
       <c r="X15">
-        <v>370.62</v>
+        <v>384.05</v>
       </c>
       <c r="Y15">
-        <v>631.0700000000001</v>
+        <v>654.02</v>
       </c>
       <c r="Z15">
         <v>140.07</v>
@@ -2264,16 +2312,16 @@
         <v>1140</v>
       </c>
       <c r="AH15" t="s">
-        <v>65</v>
+        <v>71</v>
       </c>
       <c r="AI15" t="s">
-        <v>70</v>
+        <v>78</v>
       </c>
       <c r="AJ15" t="s">
-        <v>74</v>
+        <v>85</v>
       </c>
       <c r="AK15">
-        <v>15.74661756114674</v>
+        <v>29.17980878282167</v>
       </c>
     </row>
     <row r="16" spans="1:37">
@@ -2281,109 +2329,109 @@
         <v>51</v>
       </c>
       <c r="B16">
-        <v>91.98396793587175</v>
+        <v>100</v>
       </c>
       <c r="C16">
-        <v>50</v>
+        <v>4</v>
       </c>
       <c r="D16">
-        <v>45.74</v>
+        <v>52.96</v>
       </c>
       <c r="E16">
-        <v>1.13</v>
+        <v>8.369999999999999</v>
       </c>
       <c r="F16">
-        <v>-0.9567192718065881</v>
+        <v>4.151244691231759</v>
       </c>
       <c r="G16">
-        <v>1.21</v>
+        <v>5.9</v>
       </c>
       <c r="H16">
-        <v>-1.482104682817994</v>
+        <v>4.019856777634031</v>
       </c>
       <c r="I16">
-        <v>45.98660049438477</v>
+        <v>49.75960006713867</v>
       </c>
       <c r="J16">
-        <v>45.60325031280517</v>
+        <v>38.90979995727539</v>
       </c>
       <c r="K16">
-        <v>42.91124000549316</v>
+        <v>32.67126003265381</v>
       </c>
       <c r="L16">
-        <v>39.62011703491211</v>
+        <v>26.25819499969482</v>
       </c>
       <c r="M16">
-        <v>1.01</v>
+        <v>1.28</v>
       </c>
       <c r="N16">
-        <v>1.07</v>
+        <v>1.52</v>
       </c>
       <c r="P16">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="Q16">
         <v>0</v>
       </c>
       <c r="R16">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S16">
         <v>0</v>
       </c>
       <c r="T16">
-        <v>5.555555555555555</v>
+        <v>0</v>
       </c>
       <c r="U16" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V16" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W16" t="b">
         <v>1</v>
       </c>
       <c r="X16">
-        <v>26.88</v>
+        <v>7.01</v>
       </c>
       <c r="Y16">
-        <v>46.97</v>
+        <v>55.44</v>
       </c>
       <c r="Z16">
-        <v>50.71</v>
+        <v>16.51</v>
       </c>
       <c r="AA16">
-        <v>679.46</v>
+        <v>836.36</v>
       </c>
       <c r="AB16">
-        <v>15.1</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="AC16">
-        <v>42.68</v>
+        <v>239.75</v>
       </c>
       <c r="AD16">
-        <v>10.85</v>
+        <v>9.619999999999999</v>
       </c>
       <c r="AE16">
-        <v>-8</v>
+        <v>84.8</v>
       </c>
       <c r="AF16">
-        <v>18.37</v>
+        <v>-19.13</v>
       </c>
       <c r="AG16">
-        <v>31.02</v>
+        <v>127.33</v>
       </c>
       <c r="AH16" t="s">
-        <v>56</v>
+        <v>64</v>
       </c>
       <c r="AI16" t="s">
-        <v>71</v>
+        <v>78</v>
       </c>
       <c r="AJ16" t="s">
-        <v>80</v>
+        <v>94</v>
       </c>
       <c r="AK16">
-        <v>11.03330899572033</v>
+        <v>28.74798121573899</v>
       </c>
     </row>
     <row r="17" spans="1:37">
@@ -2391,109 +2439,109 @@
         <v>52</v>
       </c>
       <c r="B17">
-        <v>96.59318637274549</v>
+        <v>91.18236472945893</v>
       </c>
       <c r="C17">
-        <v>141</v>
+        <v>57</v>
       </c>
       <c r="D17">
-        <v>76.5</v>
+        <v>48.18</v>
       </c>
       <c r="E17">
-        <v>2.21</v>
+        <v>0.96</v>
       </c>
       <c r="F17">
-        <v>1.301039832353946</v>
+        <v>-0.6052179138972744</v>
       </c>
       <c r="G17">
-        <v>1.71</v>
+        <v>0.97</v>
       </c>
       <c r="H17">
-        <v>-0.5544250212603397</v>
+        <v>-0.8098492939506416</v>
       </c>
       <c r="I17">
-        <v>76.63000030517578</v>
+        <v>47.48240051269531</v>
       </c>
       <c r="J17">
-        <v>72.31999969482422</v>
+        <v>46.03883037567139</v>
       </c>
       <c r="K17">
-        <v>71.4568000793457</v>
+        <v>45.47168022155762</v>
       </c>
       <c r="L17">
-        <v>57.60465007781983</v>
+        <v>40.9402650642395</v>
       </c>
       <c r="M17">
-        <v>1.06</v>
+        <v>1.03</v>
       </c>
       <c r="N17">
-        <v>1.07</v>
+        <v>1.04</v>
       </c>
       <c r="P17">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="Q17">
         <v>0</v>
       </c>
       <c r="R17">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S17">
         <v>0</v>
       </c>
       <c r="T17">
-        <v>0</v>
+        <v>5.555555555555555</v>
       </c>
       <c r="U17" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V17" t="b">
         <v>1</v>
       </c>
       <c r="W17" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X17">
-        <v>35.96</v>
+        <v>29.4</v>
       </c>
       <c r="Y17">
-        <v>77.45</v>
+        <v>48.79</v>
       </c>
       <c r="Z17">
-        <v>49.51</v>
+        <v>50.71</v>
       </c>
       <c r="AA17">
-        <v>-7.74</v>
+        <v>679.46</v>
       </c>
       <c r="AB17">
-        <v>10.95</v>
+        <v>15.1</v>
       </c>
       <c r="AC17">
-        <v>57.95</v>
+        <v>42.68</v>
       </c>
       <c r="AD17">
-        <v>-39.07</v>
+        <v>10.85</v>
       </c>
       <c r="AE17">
-        <v>117.19</v>
+        <v>-8</v>
       </c>
       <c r="AF17">
-        <v>-20.99</v>
+        <v>18.37</v>
       </c>
       <c r="AG17">
-        <v>-7.95</v>
+        <v>31.02</v>
       </c>
       <c r="AH17" t="s">
-        <v>67</v>
+        <v>59</v>
       </c>
       <c r="AI17" t="s">
-        <v>70</v>
+        <v>79</v>
       </c>
       <c r="AJ17" t="s">
-        <v>81</v>
+        <v>95</v>
       </c>
       <c r="AK17">
-        <v>5.620752022173512</v>
+        <v>24.71930500880479</v>
       </c>
     </row>
     <row r="18" spans="1:37">
@@ -2501,109 +2549,549 @@
         <v>53</v>
       </c>
       <c r="B18">
-        <v>96.79358717434869</v>
+        <v>90.18036072144288</v>
       </c>
       <c r="C18">
-        <v>100</v>
+        <v>488</v>
       </c>
       <c r="D18">
-        <v>58.88</v>
+        <v>508.42</v>
       </c>
       <c r="E18">
-        <v>1.34</v>
+        <v>1.26</v>
       </c>
       <c r="F18">
-        <v>-0.5177105571087062</v>
+        <v>-0.4126485776572325</v>
       </c>
       <c r="G18">
-        <v>2.65</v>
+        <v>1.08</v>
       </c>
       <c r="H18">
-        <v>1.189612742468051</v>
+        <v>-0.7020870895136611</v>
       </c>
       <c r="I18">
-        <v>59.29999923706055</v>
+        <v>509.0960083007812</v>
       </c>
       <c r="J18">
-        <v>57.28487491607666</v>
+        <v>499.3960021972656</v>
       </c>
       <c r="K18">
-        <v>53.71450012207031</v>
+        <v>485.9322009277344</v>
       </c>
       <c r="L18">
-        <v>45.04491247177124</v>
+        <v>440.3760011291504</v>
       </c>
       <c r="M18">
+        <v>1.02</v>
+      </c>
+      <c r="N18">
+        <v>1.05</v>
+      </c>
+      <c r="P18">
+        <v>5</v>
+      </c>
+      <c r="Q18">
+        <v>0</v>
+      </c>
+      <c r="R18">
+        <v>0</v>
+      </c>
+      <c r="S18">
+        <v>0</v>
+      </c>
+      <c r="T18">
+        <v>2.777777777777778</v>
+      </c>
+      <c r="U18" t="b">
+        <v>1</v>
+      </c>
+      <c r="V18" t="b">
+        <v>1</v>
+      </c>
+      <c r="W18" t="b">
+        <v>1</v>
+      </c>
+      <c r="X18">
+        <v>317.94</v>
+      </c>
+      <c r="Y18">
+        <v>520.21</v>
+      </c>
+      <c r="Z18">
+        <v>25.45</v>
+      </c>
+      <c r="AA18">
+        <v>1.92</v>
+      </c>
+      <c r="AB18">
+        <v>5.24</v>
+      </c>
+      <c r="AC18">
+        <v>127.7</v>
+      </c>
+      <c r="AD18">
+        <v>5.51</v>
+      </c>
+      <c r="AE18">
+        <v>19.93</v>
+      </c>
+      <c r="AF18">
+        <v>186.73</v>
+      </c>
+      <c r="AG18">
+        <v>-33.78</v>
+      </c>
+      <c r="AH18" t="s">
+        <v>72</v>
+      </c>
+      <c r="AI18" t="s">
+        <v>81</v>
+      </c>
+      <c r="AJ18" t="s">
+        <v>96</v>
+      </c>
+      <c r="AK18">
+        <v>22.92431947470993</v>
+      </c>
+    </row>
+    <row r="19" spans="1:37">
+      <c r="A19" t="s">
+        <v>54</v>
+      </c>
+      <c r="B19">
+        <v>94.18837675350701</v>
+      </c>
+      <c r="C19">
+        <v>297</v>
+      </c>
+      <c r="D19">
+        <v>378.22</v>
+      </c>
+      <c r="E19">
+        <v>2.59</v>
+      </c>
+      <c r="F19">
+        <v>0.4410754796736196</v>
+      </c>
+      <c r="G19">
+        <v>1.88</v>
+      </c>
+      <c r="H19">
+        <v>0.08163803366437888</v>
+      </c>
+      <c r="I19">
+        <v>376.8800048828125</v>
+      </c>
+      <c r="J19">
+        <v>359.3720001220703</v>
+      </c>
+      <c r="K19">
+        <v>336.4504016113281</v>
+      </c>
+      <c r="L19">
+        <v>311.9598501586914</v>
+      </c>
+      <c r="M19">
+        <v>1.05</v>
+      </c>
+      <c r="N19">
+        <v>1.12</v>
+      </c>
+      <c r="P19">
+        <v>3</v>
+      </c>
+      <c r="Q19">
+        <v>1</v>
+      </c>
+      <c r="R19">
+        <v>1</v>
+      </c>
+      <c r="S19">
+        <v>0</v>
+      </c>
+      <c r="T19">
+        <v>3.888888888888888</v>
+      </c>
+      <c r="U19" t="b">
+        <v>1</v>
+      </c>
+      <c r="V19" t="b">
+        <v>1</v>
+      </c>
+      <c r="W19" t="b">
+        <v>1</v>
+      </c>
+      <c r="X19">
+        <v>222.65</v>
+      </c>
+      <c r="Y19">
+        <v>384</v>
+      </c>
+      <c r="Z19">
+        <v>120.57</v>
+      </c>
+      <c r="AA19">
+        <v>5.81</v>
+      </c>
+      <c r="AB19">
+        <v>8.25</v>
+      </c>
+      <c r="AC19">
+        <v>71.29000000000001</v>
+      </c>
+      <c r="AD19">
+        <v>4.56</v>
+      </c>
+      <c r="AE19">
+        <v>46.61</v>
+      </c>
+      <c r="AF19">
+        <v>-1.67</v>
+      </c>
+      <c r="AG19">
+        <v>18.81</v>
+      </c>
+      <c r="AH19" t="s">
+        <v>73</v>
+      </c>
+      <c r="AI19" t="s">
+        <v>82</v>
+      </c>
+      <c r="AJ19" t="s">
+        <v>97</v>
+      </c>
+      <c r="AK19">
+        <v>22.70258200567183</v>
+      </c>
+    </row>
+    <row r="20" spans="1:37">
+      <c r="A20" t="s">
+        <v>55</v>
+      </c>
+      <c r="B20">
+        <v>97.99599198396794</v>
+      </c>
+      <c r="C20">
+        <v>193</v>
+      </c>
+      <c r="D20">
+        <v>82.88</v>
+      </c>
+      <c r="E20">
+        <v>2.32</v>
+      </c>
+      <c r="F20">
+        <v>0.267763077057582</v>
+      </c>
+      <c r="G20">
+        <v>1.97</v>
+      </c>
+      <c r="H20">
+        <v>0.1698071100219085</v>
+      </c>
+      <c r="I20">
+        <v>83.67000122070313</v>
+      </c>
+      <c r="J20">
+        <v>80.32800025939942</v>
+      </c>
+      <c r="K20">
+        <v>75.9368000793457</v>
+      </c>
+      <c r="L20">
+        <v>61.83420009613037</v>
+      </c>
+      <c r="M20">
         <v>1.04</v>
       </c>
-      <c r="N18">
+      <c r="N20">
         <v>1.1</v>
       </c>
-      <c r="P18">
-        <v>0</v>
-      </c>
-      <c r="Q18">
-        <v>0</v>
-      </c>
-      <c r="R18">
-        <v>0</v>
-      </c>
-      <c r="S18">
-        <v>0</v>
-      </c>
-      <c r="T18">
-        <v>0</v>
-      </c>
-      <c r="U18" t="b">
-        <v>1</v>
-      </c>
-      <c r="V18" t="b">
-        <v>0</v>
-      </c>
-      <c r="W18" t="b">
-        <v>1</v>
-      </c>
-      <c r="X18">
-        <v>27.23</v>
-      </c>
-      <c r="Y18">
-        <v>60.17</v>
-      </c>
-      <c r="Z18">
+      <c r="P20">
+        <v>0</v>
+      </c>
+      <c r="Q20">
+        <v>0</v>
+      </c>
+      <c r="R20">
+        <v>0</v>
+      </c>
+      <c r="S20">
+        <v>0</v>
+      </c>
+      <c r="T20">
+        <v>0</v>
+      </c>
+      <c r="U20" t="b">
+        <v>0</v>
+      </c>
+      <c r="V20" t="b">
+        <v>1</v>
+      </c>
+      <c r="W20" t="b">
+        <v>1</v>
+      </c>
+      <c r="X20">
+        <v>35.96</v>
+      </c>
+      <c r="Y20">
+        <v>86.45</v>
+      </c>
+      <c r="Z20">
+        <v>49.51</v>
+      </c>
+      <c r="AA20">
+        <v>-7.74</v>
+      </c>
+      <c r="AB20">
+        <v>10.95</v>
+      </c>
+      <c r="AC20">
+        <v>57.95</v>
+      </c>
+      <c r="AD20">
+        <v>-39.07</v>
+      </c>
+      <c r="AE20">
+        <v>117.19</v>
+      </c>
+      <c r="AF20">
+        <v>-20.99</v>
+      </c>
+      <c r="AG20">
+        <v>-7.95</v>
+      </c>
+      <c r="AH20" t="s">
+        <v>74</v>
+      </c>
+      <c r="AI20" t="s">
+        <v>78</v>
+      </c>
+      <c r="AJ20" t="s">
+        <v>94</v>
+      </c>
+      <c r="AK20">
+        <v>20.49085775471858</v>
+      </c>
+    </row>
+    <row r="21" spans="1:37">
+      <c r="A21" t="s">
+        <v>56</v>
+      </c>
+      <c r="B21">
+        <v>98.19639278557113</v>
+      </c>
+      <c r="C21">
+        <v>85</v>
+      </c>
+      <c r="D21">
+        <v>64.67</v>
+      </c>
+      <c r="E21">
+        <v>2.22</v>
+      </c>
+      <c r="F21">
+        <v>0.2035732983109015</v>
+      </c>
+      <c r="G21">
+        <v>1.61</v>
+      </c>
+      <c r="H21">
+        <v>-0.1828691954082095</v>
+      </c>
+      <c r="I21">
+        <v>66.45199890136719</v>
+      </c>
+      <c r="J21">
+        <v>63.47999992370605</v>
+      </c>
+      <c r="K21">
+        <v>59.24525001525879</v>
+      </c>
+      <c r="L21">
+        <v>47.36217493057251</v>
+      </c>
+      <c r="M21">
+        <v>1.05</v>
+      </c>
+      <c r="N21">
+        <v>1.12</v>
+      </c>
+      <c r="P21">
+        <v>0</v>
+      </c>
+      <c r="Q21">
+        <v>1</v>
+      </c>
+      <c r="R21">
+        <v>0</v>
+      </c>
+      <c r="S21">
+        <v>0</v>
+      </c>
+      <c r="T21">
+        <v>1.111111111111111</v>
+      </c>
+      <c r="U21" t="b">
+        <v>0</v>
+      </c>
+      <c r="V21" t="b">
+        <v>0</v>
+      </c>
+      <c r="W21" t="b">
+        <v>0</v>
+      </c>
+      <c r="X21">
+        <v>30.86</v>
+      </c>
+      <c r="Y21">
+        <v>68.22</v>
+      </c>
+      <c r="Z21">
         <v>14.61</v>
       </c>
-      <c r="AA18">
+      <c r="AA21">
         <v>58.19</v>
       </c>
-      <c r="AB18">
+      <c r="AB21">
         <v>18.69</v>
       </c>
-      <c r="AC18">
+      <c r="AC21">
         <v>26.62</v>
       </c>
-      <c r="AD18">
+      <c r="AD21">
         <v>8.380000000000001</v>
       </c>
-      <c r="AE18">
+      <c r="AE21">
         <v>10.69</v>
       </c>
-      <c r="AF18">
+      <c r="AF21">
         <v>11.97</v>
       </c>
-      <c r="AG18">
+      <c r="AG21">
         <v>2.16</v>
       </c>
-      <c r="AH18" t="s">
-        <v>68</v>
-      </c>
-      <c r="AI18" t="s">
+      <c r="AH21" t="s">
+        <v>75</v>
+      </c>
+      <c r="AI21" t="s">
+        <v>78</v>
+      </c>
+      <c r="AJ21" t="s">
+        <v>94</v>
+      </c>
+      <c r="AK21">
+        <v>19.80140119800624</v>
+      </c>
+    </row>
+    <row r="22" spans="1:37">
+      <c r="A22" t="s">
+        <v>57</v>
+      </c>
+      <c r="B22">
+        <v>93.78757515030061</v>
+      </c>
+      <c r="C22">
+        <v>476</v>
+      </c>
+      <c r="D22">
+        <v>895.64</v>
+      </c>
+      <c r="E22">
+        <v>1.24</v>
+      </c>
+      <c r="F22">
+        <v>-0.4254865334065686</v>
+      </c>
+      <c r="G22">
+        <v>1.17</v>
+      </c>
+      <c r="H22">
+        <v>-0.6139180131561316</v>
+      </c>
+      <c r="I22">
+        <v>894.25400390625</v>
+      </c>
+      <c r="J22">
+        <v>855.5260009765625</v>
+      </c>
+      <c r="K22">
+        <v>829.6826000976563</v>
+      </c>
+      <c r="L22">
+        <v>744.0111502075196</v>
+      </c>
+      <c r="M22">
+        <v>1.05</v>
+      </c>
+      <c r="N22">
+        <v>1.08</v>
+      </c>
+      <c r="P22">
+        <v>7</v>
+      </c>
+      <c r="Q22">
+        <v>1</v>
+      </c>
+      <c r="R22">
+        <v>0</v>
+      </c>
+      <c r="S22">
+        <v>0</v>
+      </c>
+      <c r="T22">
+        <v>5</v>
+      </c>
+      <c r="U22" t="b">
+        <v>0</v>
+      </c>
+      <c r="V22" t="b">
+        <v>1</v>
+      </c>
+      <c r="W22" t="b">
+        <v>0</v>
+      </c>
+      <c r="X22">
+        <v>573.71</v>
+      </c>
+      <c r="Y22">
+        <v>922.5</v>
+      </c>
+      <c r="Z22">
+        <v>34.66</v>
+      </c>
+      <c r="AA22">
+        <v>2.66</v>
+      </c>
+      <c r="AB22">
+        <v>1.01</v>
+      </c>
+      <c r="AC22">
+        <v>24.93</v>
+      </c>
+      <c r="AD22">
+        <v>14.58</v>
+      </c>
+      <c r="AE22">
+        <v>1.61</v>
+      </c>
+      <c r="AF22">
+        <v>-3.52</v>
+      </c>
+      <c r="AG22">
+        <v>27.44</v>
+      </c>
+      <c r="AH22" t="s">
         <v>70</v>
       </c>
-      <c r="AJ18" t="s">
-        <v>81</v>
-      </c>
-      <c r="AK18">
-        <v>5.507262172816827</v>
+      <c r="AI22" t="s">
+        <v>80</v>
+      </c>
+      <c r="AJ22" t="s">
+        <v>98</v>
+      </c>
+      <c r="AK22">
+        <v>3.600000000000001</v>
       </c>
     </row>
   </sheetData>
